--- a/shared/Feedback_Analysis.xlsx
+++ b/shared/Feedback_Analysis.xlsx
@@ -20,8 +20,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd hh:mm"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd hh:mm"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -77,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -85,7 +85,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -96,6 +96,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -517,23 +523,23 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="9" t="n">
         <v>46309.54555740702</v>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>Fathima Nourin</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>Accutech Automation</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>nouriii2025@gmail.com</t>
         </is>
@@ -541,7 +547,7 @@
       <c r="F2" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -674,7 +680,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 13:05</t>
+          <t>2026-10-14 15:58</t>
         </is>
       </c>
     </row>
